--- a/output/roomself_excel/5861.xlsx
+++ b/output/roomself_excel/5861.xlsx
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>57570</v>
+        <v>104442</v>
       </c>
       <c r="D2" t="n">
-        <v>1972</v>
+        <v>2588</v>
       </c>
       <c r="E2" t="n">
-        <v>331</v>
+        <v>367</v>
       </c>
       <c r="F2" t="n">
-        <v>204</v>
+        <v>367</v>
       </c>
     </row>
     <row r="3">
@@ -488,17 +488,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>35856</v>
+        <v>25781</v>
       </c>
       <c r="D3" t="n">
-        <v>1572</v>
+        <v>1320</v>
       </c>
       <c r="E3" t="n">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="F3" t="n">
         <v>29</v>
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>468698</v>
+        <v>57570</v>
       </c>
       <c r="D4" t="n">
-        <v>6144</v>
+        <v>1972</v>
       </c>
       <c r="E4" t="n">
-        <v>1214</v>
+        <v>331</v>
       </c>
       <c r="F4" t="n">
-        <v>834</v>
+        <v>204</v>
       </c>
     </row>
     <row r="5">
@@ -532,17 +532,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>25781</v>
+        <v>35856</v>
       </c>
       <c r="D5" t="n">
-        <v>1320</v>
+        <v>1572</v>
       </c>
       <c r="E5" t="n">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="F5" t="n">
         <v>29</v>
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>104442</v>
+        <v>468698</v>
       </c>
       <c r="D6" t="n">
-        <v>2588</v>
+        <v>6144</v>
       </c>
       <c r="E6" t="n">
-        <v>367</v>
+        <v>834</v>
       </c>
       <c r="F6" t="n">
-        <v>367</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7">
@@ -608,7 +608,7 @@
         <v>3772</v>
       </c>
       <c r="E8" t="n">
-        <v>779</v>
+        <v>500</v>
       </c>
       <c r="F8" t="n">
         <v>497</v>
@@ -630,10 +630,10 @@
         <v>1800</v>
       </c>
       <c r="E9" t="n">
-        <v>369</v>
+        <v>184</v>
       </c>
       <c r="F9" t="n">
-        <v>251</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">

--- a/output/roomself_excel/5861.xlsx
+++ b/output/roomself_excel/5861.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:Y10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,107 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_4</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_4</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_4</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_5</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_5</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_5</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_6</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_6</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_6</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_7</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_7</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_7</t>
         </is>
       </c>
     </row>
@@ -475,12 +570,43 @@
       <c r="D2" t="n">
         <v>2588</v>
       </c>
-      <c r="E2" t="n">
-        <v>367</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>367</v>
-      </c>
+        <v>511</v>
+      </c>
+      <c r="G2" t="n">
+        <v>29</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>309</v>
+      </c>
+      <c r="J2" t="n">
+        <v>29</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +623,35 @@
       <c r="D3" t="n">
         <v>1320</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>127</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>29</v>
       </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +668,43 @@
       <c r="D4" t="n">
         <v>1972</v>
       </c>
-      <c r="E4" t="n">
-        <v>331</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>204</v>
-      </c>
+        <v>380</v>
+      </c>
+      <c r="G4" t="n">
+        <v>14</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>303</v>
+      </c>
+      <c r="J4" t="n">
+        <v>14</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +721,35 @@
       <c r="D5" t="n">
         <v>1572</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>144</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>29</v>
       </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +766,59 @@
       <c r="D6" t="n">
         <v>6144</v>
       </c>
-      <c r="E6" t="n">
-        <v>834</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>808</v>
-      </c>
+        <v>306</v>
+      </c>
+      <c r="G6" t="n">
+        <v>29</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>479</v>
+      </c>
+      <c r="J6" t="n">
+        <v>24</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>443</v>
+      </c>
+      <c r="M6" t="n">
+        <v>29</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>755</v>
+      </c>
+      <c r="P6" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +835,35 @@
       <c r="D7" t="n">
         <v>2752</v>
       </c>
-      <c r="E7" t="n">
-        <v>299</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>104</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="G7" t="n">
+        <v>15</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,11 +880,82 @@
       <c r="D8" t="n">
         <v>3772</v>
       </c>
-      <c r="E8" t="n">
-        <v>500</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F8" t="n">
-        <v>497</v>
+        <v>699</v>
+      </c>
+      <c r="G8" t="n">
+        <v>16</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>152</v>
+      </c>
+      <c r="J8" t="n">
+        <v>16</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>173</v>
+      </c>
+      <c r="M8" t="n">
+        <v>17</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>97</v>
+      </c>
+      <c r="P8" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>56</v>
+      </c>
+      <c r="S8" t="n">
+        <v>28</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="U8" t="n">
+        <v>32</v>
+      </c>
+      <c r="V8" t="n">
+        <v>29</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>50</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="9">
@@ -629,12 +973,35 @@
       <c r="D9" t="n">
         <v>1800</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>184</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>16</v>
       </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +1018,43 @@
       <c r="D10" t="n">
         <v>1520</v>
       </c>
-      <c r="E10" t="n">
-        <v>239</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F10" t="n">
-        <v>173</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="G10" t="n">
+        <v>16</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>223</v>
+      </c>
+      <c r="J10" t="n">
+        <v>16</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/roomself_excel/5861.xlsx
+++ b/output/roomself_excel/5861.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y10"/>
+  <dimension ref="A1:BI10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -552,6 +552,186 @@
       <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>ExtWallWidth_7</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_1</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_1</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_1</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_1</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_2</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_2</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_2</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_2</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_3</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_3</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_3</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_3</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_4</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_4</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_4</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_4</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_5</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_5</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_5</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_5</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_6</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_6</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_6</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_6</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_7</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_7</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_7</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_7</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_8</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_8</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_8</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_8</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_9</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_9</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_9</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_9</t>
         </is>
       </c>
     </row>
@@ -607,6 +787,66 @@
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
+        <v>182</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>29</v>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>160</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>29</v>
+      </c>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -652,6 +892,54 @@
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>41</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>29</v>
+      </c>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr"/>
+      <c r="BA3" t="inlineStr"/>
+      <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="inlineStr"/>
+      <c r="BD3" t="inlineStr"/>
+      <c r="BE3" t="inlineStr"/>
+      <c r="BF3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr"/>
+      <c r="BH3" t="inlineStr"/>
+      <c r="BI3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -705,6 +993,66 @@
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>89</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AF4" t="n">
+        <v>84</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr"/>
+      <c r="BA4" t="inlineStr"/>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr"/>
+      <c r="BH4" t="inlineStr"/>
+      <c r="BI4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -750,6 +1098,54 @@
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>36</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>29</v>
+      </c>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr"/>
+      <c r="BH5" t="inlineStr"/>
+      <c r="BI5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -819,6 +1215,126 @@
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>203</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>29</v>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>84</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>24</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
+        <v>88</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="AN6" t="n">
+        <v>168</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>24</v>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="AR6" t="n">
+        <v>215</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>29</v>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AV6" t="n">
+        <v>504</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>24</v>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AZ6" t="n">
+        <v>163</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>24</v>
+      </c>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr"/>
+      <c r="BH6" t="inlineStr"/>
+      <c r="BI6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -864,6 +1380,42 @@
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr"/>
+      <c r="AX7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr"/>
+      <c r="BA7" t="inlineStr"/>
+      <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="inlineStr"/>
+      <c r="BD7" t="inlineStr"/>
+      <c r="BE7" t="inlineStr"/>
+      <c r="BF7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr"/>
+      <c r="BH7" t="inlineStr"/>
+      <c r="BI7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -956,6 +1508,150 @@
       </c>
       <c r="Y8" t="n">
         <v>33</v>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>222</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="AF8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
+        <v>35</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AN8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="AR8" t="n">
+        <v>150</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>17</v>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AV8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AZ8" t="n">
+        <v>62</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="BD8" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="BH8" t="n">
+        <v>69</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="9">
@@ -1002,6 +1698,54 @@
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>34</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr"/>
+      <c r="AX9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr"/>
+      <c r="BA9" t="inlineStr"/>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr"/>
+      <c r="BH9" t="inlineStr"/>
+      <c r="BI9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1055,6 +1799,54 @@
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>73</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr"/>
+      <c r="BA10" t="inlineStr"/>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="inlineStr"/>
+      <c r="BF10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr"/>
+      <c r="BH10" t="inlineStr"/>
+      <c r="BI10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
